--- a/Cronograma/Plantilla_Itinerario _PPP_pasantias_v4.xlsx
+++ b/Cronograma/Plantilla_Itinerario _PPP_pasantias_v4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Downloads\metodologia\tallos\SLR_SmartAgriculture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ariel\Documents\7_semestre\PPP\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C121144-0960-4F06-99AA-FDEFEBB0D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD4C865-FAF5-4A40-8873-3479C75664FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,9 +266,6 @@
     <t>1. Inducción al proyecto de investigación</t>
   </si>
   <si>
-    <t>Laboratorio de Investigación de Software</t>
-  </si>
-  <si>
     <t>Desarrollo de Software(Desarrollo de una app movil que detecte enfermedades en tallos de aguacate)</t>
   </si>
   <si>
@@ -864,6 +861,9 @@
   </si>
   <si>
     <t>14. Partición de datos del modelo de IA</t>
+  </si>
+  <si>
+    <t>Departamente de computacion de Investigación de Software</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1050,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1124,9 +1124,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1452,7 +1449,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.5">
@@ -1460,7 +1457,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="36" x14ac:dyDescent="0.5">
@@ -1468,7 +1465,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -1525,7 +1522,7 @@
         <v>46286</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>69</v>
@@ -1548,7 +1545,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" s="21">
         <v>2</v>
@@ -1569,10 +1566,10 @@
         <v>46287</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>103</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>104</v>
       </c>
       <c r="D12" s="21">
         <v>2</v>
@@ -1589,10 +1586,10 @@
         <v>46288</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>105</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>106</v>
       </c>
       <c r="D13" s="21">
         <v>2</v>
@@ -1613,10 +1610,10 @@
         <v>46288</v>
       </c>
       <c r="B14" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>107</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>108</v>
       </c>
       <c r="D14" s="21">
         <v>2</v>
@@ -1636,7 +1633,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" s="21">
         <v>2</v>
@@ -1657,10 +1654,10 @@
         <v>46289</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>110</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>111</v>
       </c>
       <c r="D16" s="21">
         <v>2</v>
@@ -1677,10 +1674,10 @@
         <v>46290</v>
       </c>
       <c r="B17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>112</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>113</v>
       </c>
       <c r="D17" s="21">
         <v>2</v>
@@ -1701,10 +1698,10 @@
         <v>46290</v>
       </c>
       <c r="B18" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>114</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>115</v>
       </c>
       <c r="D18" s="21">
         <v>2</v>
@@ -1724,7 +1721,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" s="21">
         <v>2</v>
@@ -1745,10 +1742,10 @@
         <v>46293</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>117</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>118</v>
       </c>
       <c r="D20" s="21">
         <v>2</v>
@@ -1765,10 +1762,10 @@
         <v>46294</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>119</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>120</v>
       </c>
       <c r="D21" s="21">
         <v>2</v>
@@ -1789,10 +1786,10 @@
         <v>46294</v>
       </c>
       <c r="B22" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>121</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>122</v>
       </c>
       <c r="D22" s="21">
         <v>2</v>
@@ -1812,7 +1809,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="21">
         <v>2</v>
@@ -1833,10 +1830,10 @@
         <v>46295</v>
       </c>
       <c r="B24" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>124</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>125</v>
       </c>
       <c r="D24" s="21">
         <v>2</v>
@@ -1856,7 +1853,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="21">
         <v>2</v>
@@ -1877,10 +1874,10 @@
         <v>46296</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>127</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>128</v>
       </c>
       <c r="D26" s="21">
         <v>2</v>
@@ -1897,10 +1894,10 @@
         <v>46297</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>129</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>130</v>
       </c>
       <c r="D27" s="21">
         <v>2</v>
@@ -1921,10 +1918,10 @@
         <v>46297</v>
       </c>
       <c r="B28" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>131</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>132</v>
       </c>
       <c r="D28" s="21">
         <v>2</v>
@@ -1944,7 +1941,7 @@
         <v>21</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" s="21">
         <v>2</v>
@@ -1965,10 +1962,10 @@
         <v>46300</v>
       </c>
       <c r="B30" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>134</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>135</v>
       </c>
       <c r="D30" s="21">
         <v>2</v>
@@ -1988,7 +1985,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" s="21">
         <v>2</v>
@@ -2009,10 +2006,10 @@
         <v>46301</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>137</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>138</v>
       </c>
       <c r="D32" s="21">
         <v>2</v>
@@ -2029,10 +2026,10 @@
         <v>46302</v>
       </c>
       <c r="B33" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>139</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>140</v>
       </c>
       <c r="D33" s="21">
         <v>2</v>
@@ -2053,10 +2050,10 @@
         <v>46302</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>141</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>142</v>
       </c>
       <c r="D34" s="21">
         <v>2</v>
@@ -2097,7 +2094,7 @@
         <v>46303</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>25</v>
@@ -2117,10 +2114,10 @@
         <v>46307</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>90</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>91</v>
       </c>
       <c r="D37" s="21">
         <v>2</v>
@@ -2141,10 +2138,10 @@
         <v>46307</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="21">
         <v>2</v>
@@ -2161,10 +2158,10 @@
         <v>46308</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" s="21">
         <v>2</v>
@@ -2185,10 +2182,10 @@
         <v>46308</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D40" s="21">
         <v>2</v>
@@ -2205,10 +2202,10 @@
         <v>46309</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D41" s="21">
         <v>2</v>
@@ -2229,10 +2226,10 @@
         <v>46309</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D42" s="21">
         <v>2</v>
@@ -2249,10 +2246,10 @@
         <v>46310</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D43" s="21">
         <v>2</v>
@@ -2273,10 +2270,10 @@
         <v>46310</v>
       </c>
       <c r="B44" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>149</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>150</v>
       </c>
       <c r="D44" s="21">
         <v>2</v>
@@ -2293,10 +2290,10 @@
         <v>46311</v>
       </c>
       <c r="B45" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>152</v>
       </c>
       <c r="D45" s="21">
         <v>2</v>
@@ -2317,10 +2314,10 @@
         <v>46311</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" s="21">
         <v>2</v>
@@ -2337,10 +2334,10 @@
         <v>46314</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D47" s="21">
         <v>2</v>
@@ -2361,10 +2358,10 @@
         <v>46314</v>
       </c>
       <c r="B48" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>155</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>156</v>
       </c>
       <c r="D48" s="21">
         <v>2</v>
@@ -2381,10 +2378,10 @@
         <v>46315</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D49" s="21">
         <v>2</v>
@@ -2405,10 +2402,10 @@
         <v>46315</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" s="21">
         <v>2</v>
@@ -2425,7 +2422,7 @@
         <v>46316</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C51" s="21" t="s">
         <v>26</v>
@@ -2449,7 +2446,7 @@
         <v>46316</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C52" s="21" t="s">
         <v>27</v>
@@ -2469,10 +2466,10 @@
         <v>46317</v>
       </c>
       <c r="B53" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>161</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>162</v>
       </c>
       <c r="D53" s="21">
         <v>2</v>
@@ -2493,10 +2490,10 @@
         <v>46317</v>
       </c>
       <c r="B54" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>164</v>
       </c>
       <c r="D54" s="21">
         <v>2</v>
@@ -2509,14 +2506,14 @@
       <c r="H54" s="21"/>
     </row>
     <row r="55" spans="1:8" ht="36" x14ac:dyDescent="0.5">
-      <c r="A55" s="26">
+      <c r="A55" s="22">
         <v>46318</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55" s="21">
         <v>2</v>
@@ -2533,14 +2530,14 @@
       <c r="H55" s="21"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A56" s="26">
+      <c r="A56" s="22">
         <v>46318</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D56" s="21">
         <v>2</v>
@@ -2557,7 +2554,7 @@
         <v>46321</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="21" t="s">
         <v>28</v>
@@ -2581,7 +2578,7 @@
         <v>46321</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="21" t="s">
         <v>29</v>
@@ -2601,7 +2598,7 @@
         <v>46322</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C59" s="21" t="s">
         <v>30</v>
@@ -2625,7 +2622,7 @@
         <v>46322</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C60" s="21" t="s">
         <v>31</v>
@@ -2645,7 +2642,7 @@
         <v>46323</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" s="21" t="s">
         <v>32</v>
@@ -2669,7 +2666,7 @@
         <v>46323</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C62" s="21" t="s">
         <v>33</v>
@@ -2689,7 +2686,7 @@
         <v>46324</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C63" s="21" t="s">
         <v>34</v>
@@ -2713,7 +2710,7 @@
         <v>46324</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C64" s="21" t="s">
         <v>35</v>
@@ -2733,10 +2730,10 @@
         <v>46325</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D65" s="21">
         <v>2</v>
@@ -2757,7 +2754,7 @@
         <v>46325</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="21" t="s">
         <v>36</v>
@@ -2777,7 +2774,7 @@
         <v>46329</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C67" s="21" t="s">
         <v>37</v>
@@ -2801,7 +2798,7 @@
         <v>46329</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C68" s="21" t="s">
         <v>38</v>
@@ -2821,7 +2818,7 @@
         <v>46330</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69" s="21" t="s">
         <v>39</v>
@@ -2845,7 +2842,7 @@
         <v>46330</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C70" s="21" t="s">
         <v>40</v>
@@ -2865,7 +2862,7 @@
         <v>46331</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C71" s="21" t="s">
         <v>41</v>
@@ -2889,7 +2886,7 @@
         <v>46331</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C72" s="21" t="s">
         <v>42</v>
@@ -2909,7 +2906,7 @@
         <v>46332</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C73" s="21" t="s">
         <v>43</v>
@@ -2933,7 +2930,7 @@
         <v>46332</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C74" s="21" t="s">
         <v>44</v>
@@ -2953,7 +2950,7 @@
         <v>46335</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C75" s="21" t="s">
         <v>45</v>
@@ -2977,10 +2974,10 @@
         <v>46335</v>
       </c>
       <c r="B76" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C76" s="21" t="s">
         <v>181</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>182</v>
       </c>
       <c r="D76" s="21">
         <v>2</v>
@@ -2997,7 +2994,7 @@
         <v>46336</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C77" s="21" t="s">
         <v>46</v>
@@ -3021,10 +3018,10 @@
         <v>46336</v>
       </c>
       <c r="B78" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="21" t="s">
         <v>184</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>185</v>
       </c>
       <c r="D78" s="21">
         <v>2</v>
@@ -3041,10 +3038,10 @@
         <v>46337</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D79" s="21">
         <v>2</v>
@@ -3065,10 +3062,10 @@
         <v>46337</v>
       </c>
       <c r="B80" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="21" t="s">
         <v>187</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>188</v>
       </c>
       <c r="D80" s="21">
         <v>2</v>
@@ -3085,10 +3082,10 @@
         <v>46338</v>
       </c>
       <c r="B81" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="21" t="s">
         <v>189</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>190</v>
       </c>
       <c r="D81" s="21">
         <v>2</v>
@@ -3109,10 +3106,10 @@
         <v>46338</v>
       </c>
       <c r="B82" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C82" s="21" t="s">
         <v>191</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>192</v>
       </c>
       <c r="D82" s="21">
         <v>2</v>
@@ -3129,10 +3126,10 @@
         <v>46339</v>
       </c>
       <c r="B83" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C83" s="21" t="s">
         <v>193</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>194</v>
       </c>
       <c r="D83" s="21">
         <v>2</v>
@@ -3153,10 +3150,10 @@
         <v>46339</v>
       </c>
       <c r="B84" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="C84" s="21" t="s">
         <v>195</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>196</v>
       </c>
       <c r="D84" s="21">
         <v>2</v>
@@ -3173,7 +3170,7 @@
         <v>46342</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" s="21" t="s">
         <v>47</v>
@@ -3197,10 +3194,10 @@
         <v>46342</v>
       </c>
       <c r="B86" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" s="21" t="s">
         <v>197</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>198</v>
       </c>
       <c r="D86" s="21">
         <v>2</v>
@@ -3217,10 +3214,10 @@
         <v>46343</v>
       </c>
       <c r="B87" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" s="21" t="s">
         <v>199</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>200</v>
       </c>
       <c r="D87" s="21">
         <v>2</v>
@@ -3241,10 +3238,10 @@
         <v>46343</v>
       </c>
       <c r="B88" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C88" s="21" t="s">
         <v>201</v>
-      </c>
-      <c r="C88" s="21" t="s">
-        <v>202</v>
       </c>
       <c r="D88" s="21">
         <v>2</v>
@@ -3261,10 +3258,10 @@
         <v>46344</v>
       </c>
       <c r="B89" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C89" s="21" t="s">
         <v>203</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>204</v>
       </c>
       <c r="D89" s="21">
         <v>2</v>
@@ -3285,7 +3282,7 @@
         <v>46344</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C90" s="21" t="s">
         <v>48</v>
@@ -3305,7 +3302,7 @@
         <v>46345</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" s="21" t="s">
         <v>49</v>
@@ -3329,10 +3326,10 @@
         <v>46345</v>
       </c>
       <c r="B92" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="C92" s="21" t="s">
         <v>207</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>208</v>
       </c>
       <c r="D92" s="21">
         <v>2</v>
@@ -3349,10 +3346,10 @@
         <v>46346</v>
       </c>
       <c r="B93" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C93" s="21" t="s">
         <v>209</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>210</v>
       </c>
       <c r="D93" s="21">
         <v>2</v>
@@ -3373,10 +3370,10 @@
         <v>46346</v>
       </c>
       <c r="B94" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C94" s="21" t="s">
         <v>211</v>
-      </c>
-      <c r="C94" s="21" t="s">
-        <v>212</v>
       </c>
       <c r="D94" s="21">
         <v>2</v>
@@ -3393,7 +3390,7 @@
         <v>46349</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C95" s="21" t="s">
         <v>50</v>
@@ -3417,7 +3414,7 @@
         <v>46349</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C96" s="21" t="s">
         <v>51</v>
@@ -3437,10 +3434,10 @@
         <v>46350</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D97" s="21">
         <v>2</v>
@@ -3461,7 +3458,7 @@
         <v>46350</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C98" s="21" t="s">
         <v>52</v>
@@ -3481,7 +3478,7 @@
         <v>46351</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="21" t="s">
         <v>53</v>
@@ -3505,10 +3502,10 @@
         <v>46351</v>
       </c>
       <c r="B100" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="21" t="s">
         <v>218</v>
-      </c>
-      <c r="C100" s="21" t="s">
-        <v>219</v>
       </c>
       <c r="D100" s="21">
         <v>2</v>
@@ -3525,7 +3522,7 @@
         <v>46352</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C101" s="21" t="s">
         <v>54</v>
@@ -3549,7 +3546,7 @@
         <v>46352</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C102" s="21" t="s">
         <v>55</v>
@@ -3569,7 +3566,7 @@
         <v>46353</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C103" s="21" t="s">
         <v>56</v>
@@ -3593,10 +3590,10 @@
         <v>46353</v>
       </c>
       <c r="B104" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C104" s="21" t="s">
         <v>222</v>
-      </c>
-      <c r="C104" s="21" t="s">
-        <v>223</v>
       </c>
       <c r="D104" s="21">
         <v>2</v>
@@ -3613,7 +3610,7 @@
         <v>46356</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C105" s="21" t="s">
         <v>57</v>
@@ -3637,10 +3634,10 @@
         <v>46356</v>
       </c>
       <c r="B106" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" s="21" t="s">
         <v>225</v>
-      </c>
-      <c r="C106" s="21" t="s">
-        <v>226</v>
       </c>
       <c r="D106" s="21">
         <v>2</v>
@@ -3657,10 +3654,10 @@
         <v>46357</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D107" s="21">
         <v>2</v>
@@ -3681,7 +3678,7 @@
         <v>46357</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C108" s="21" t="s">
         <v>58</v>
@@ -3701,10 +3698,10 @@
         <v>46358</v>
       </c>
       <c r="B109" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="C109" s="21" t="s">
         <v>229</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>230</v>
       </c>
       <c r="D109" s="21">
         <v>2</v>
@@ -3725,7 +3722,7 @@
         <v>46358</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C110" s="21" t="s">
         <v>59</v>
@@ -3745,10 +3742,10 @@
         <v>46359</v>
       </c>
       <c r="B111" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="21" t="s">
         <v>232</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>233</v>
       </c>
       <c r="D111" s="21">
         <v>2</v>
@@ -3769,7 +3766,7 @@
         <v>46359</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C112" s="21" t="s">
         <v>60</v>
@@ -3789,7 +3786,7 @@
         <v>46360</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C113" s="21" t="s">
         <v>61</v>
@@ -3813,10 +3810,10 @@
         <v>46360</v>
       </c>
       <c r="B114" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="C114" s="21" t="s">
         <v>236</v>
-      </c>
-      <c r="C114" s="21" t="s">
-        <v>237</v>
       </c>
       <c r="D114" s="21">
         <v>2</v>
@@ -3833,7 +3830,7 @@
         <v>46363</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C115" s="21" t="s">
         <v>62</v>
@@ -3857,10 +3854,10 @@
         <v>46363</v>
       </c>
       <c r="B116" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="C116" s="21" t="s">
         <v>238</v>
-      </c>
-      <c r="C116" s="21" t="s">
-        <v>239</v>
       </c>
       <c r="D116" s="21">
         <v>2</v>
@@ -3877,7 +3874,7 @@
         <v>46364</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C117" s="21" t="s">
         <v>63</v>
@@ -3901,10 +3898,10 @@
         <v>46364</v>
       </c>
       <c r="B118" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C118" s="21" t="s">
         <v>241</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>242</v>
       </c>
       <c r="D118" s="21">
         <v>2</v>
@@ -3921,7 +3918,7 @@
         <v>46365</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C119" s="21" t="s">
         <v>64</v>
@@ -3945,7 +3942,7 @@
         <v>46365</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C120" s="21" t="s">
         <v>65</v>
@@ -3965,10 +3962,10 @@
         <v>46366</v>
       </c>
       <c r="B121" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="C121" s="21" t="s">
         <v>244</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>245</v>
       </c>
       <c r="D121" s="21">
         <v>2</v>
@@ -3989,10 +3986,10 @@
         <v>46366</v>
       </c>
       <c r="B122" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="C122" s="21" t="s">
         <v>246</v>
-      </c>
-      <c r="C122" s="21" t="s">
-        <v>247</v>
       </c>
       <c r="D122" s="21">
         <v>2</v>
@@ -4009,7 +4006,7 @@
         <v>46367</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C123" s="21" t="s">
         <v>66</v>
@@ -4033,7 +4030,7 @@
         <v>46367</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C124" s="21" t="s">
         <v>67</v>
@@ -4053,10 +4050,10 @@
         <v>46370</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D125" s="21">
         <v>2</v>
@@ -4077,10 +4074,10 @@
         <v>46370</v>
       </c>
       <c r="B126" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" s="21" t="s">
         <v>251</v>
-      </c>
-      <c r="C126" s="21" t="s">
-        <v>252</v>
       </c>
       <c r="D126" s="21">
         <v>2</v>
@@ -4097,10 +4094,10 @@
         <v>46371</v>
       </c>
       <c r="B127" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" s="21" t="s">
         <v>253</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>254</v>
       </c>
       <c r="D127" s="21">
         <v>2</v>
@@ -4121,10 +4118,10 @@
         <v>46371</v>
       </c>
       <c r="B128" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C128" s="21" t="s">
         <v>255</v>
-      </c>
-      <c r="C128" s="21" t="s">
-        <v>256</v>
       </c>
       <c r="D128" s="21">
         <v>2</v>
@@ -4141,10 +4138,10 @@
         <v>46372</v>
       </c>
       <c r="B129" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="21" t="s">
         <v>257</v>
-      </c>
-      <c r="C129" s="21" t="s">
-        <v>258</v>
       </c>
       <c r="D129" s="21">
         <v>2</v>
@@ -4165,10 +4162,10 @@
         <v>46372</v>
       </c>
       <c r="B130" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>260</v>
       </c>
       <c r="D130" s="21">
         <v>2</v>
@@ -4185,10 +4182,10 @@
         <v>46373</v>
       </c>
       <c r="B131" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" s="21" t="s">
         <v>261</v>
-      </c>
-      <c r="C131" s="21" t="s">
-        <v>262</v>
       </c>
       <c r="D131" s="21">
         <v>2</v>
@@ -4209,10 +4206,10 @@
         <v>46373</v>
       </c>
       <c r="B132" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" s="21" t="s">
         <v>263</v>
-      </c>
-      <c r="C132" s="21" t="s">
-        <v>264</v>
       </c>
       <c r="D132" s="21">
         <v>2</v>
@@ -4229,10 +4226,10 @@
         <v>46374</v>
       </c>
       <c r="B133" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="C133" s="21" t="s">
-        <v>266</v>
       </c>
       <c r="D133" s="21">
         <v>2</v>
@@ -4253,10 +4250,10 @@
         <v>46374</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D134" s="21">
         <v>2</v>
@@ -4370,9 +4367,6 @@
     </row>
   </sheetData>
   <mergeCells count="127">
-    <mergeCell ref="E109:E110"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="E111:E112"/>
     <mergeCell ref="G63:G64"/>
     <mergeCell ref="E65:E66"/>
     <mergeCell ref="G71:G72"/>
@@ -4385,8 +4379,15 @@
     <mergeCell ref="E83:E84"/>
     <mergeCell ref="G83:G84"/>
     <mergeCell ref="G95:G96"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="E75:E76"/>
     <mergeCell ref="E57:E58"/>
     <mergeCell ref="E49:E50"/>
     <mergeCell ref="G49:G50"/>
@@ -4400,18 +4401,12 @@
     <mergeCell ref="G57:G58"/>
     <mergeCell ref="G59:G60"/>
     <mergeCell ref="E37:E38"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="G77:G78"/>
     <mergeCell ref="G37:G38"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="G39:G40"/>
     <mergeCell ref="E41:E42"/>
     <mergeCell ref="G41:G42"/>
     <mergeCell ref="E43:E44"/>
-    <mergeCell ref="G43:G44"/>
     <mergeCell ref="G45:G46"/>
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="G47:G48"/>
@@ -4420,6 +4415,11 @@
     <mergeCell ref="E51:E52"/>
     <mergeCell ref="E45:E46"/>
     <mergeCell ref="G29:G30"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="E23:E24"/>
     <mergeCell ref="E61:E62"/>
     <mergeCell ref="G61:G62"/>
     <mergeCell ref="E63:E64"/>
@@ -4443,13 +4443,7 @@
     <mergeCell ref="G33:G34"/>
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="G35:G36"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="G67:G68"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="G43:G44"/>
     <mergeCell ref="E77:E78"/>
     <mergeCell ref="E79:E80"/>
     <mergeCell ref="G79:G80"/>
@@ -4480,6 +4474,9 @@
     <mergeCell ref="G115:G116"/>
     <mergeCell ref="E117:E118"/>
     <mergeCell ref="G117:G118"/>
+    <mergeCell ref="E109:E110"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="E111:E112"/>
     <mergeCell ref="E119:E120"/>
     <mergeCell ref="G119:G120"/>
     <mergeCell ref="E121:E122"/>
